--- a/assets/docs/lop5/Dao duc - Lop 5.xlsx
+++ b/assets/docs/lop5/Dao duc - Lop 5.xlsx
@@ -805,7 +805,8 @@
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>NLS-KT (Cơ bản 2): Ở bài “Vượt qua khó khăn”, GV chiếu một hai câu chuyện có thật về tấm gương vượt khó do thầy cô.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở bài “Vượt qua khó khăn”, GV chiếu một hai câu chuyện có thật về tấm gương vượt khó do thầy cô chọn từ nguồn tin cậy, kèm ảnh minh hoạ; HS đọc
+Năng lực số Miền 2 (Cơ bản, bậc 2): GV gõ lên màn hình những khó khăn HS nêu cùng cách khắc phục mà các bạn góp ý, thành bảng hai cột</t>
         </is>
       </c>
     </row>
